--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -413,22 +413,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,259 +446,2691 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>Short Name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>City</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>Organizer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Venue</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Ticket Info</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Source URL</t>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Confidence Score</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Last Checked At</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WLGA Strategic Innovation Summit 2026</t>
+          <t>Pipeline &amp; Gas Expo 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11–12 Mart</t>
+          <t>Pipeline &amp; Gas Expo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Japonya</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>asia</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>lpg</t>
+          <t>İtalya</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>World Liquid Gas Association</t>
+          <t>eu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>dist</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.worldliquidgas.org</t>
+          <t>Piacenza Expo – Le Mose</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Check official site</t>
+          <t>Mediapoint &amp; Exhibitions s.r.l.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0.93</v>
+          <t>https://www.pipelineandgasexpo.com</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Ziyaretçi girişi ücretsiz (kayıt gerekli)</t>
+        </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.worldliquidgas.org/events/</t>
-        </is>
-      </c>
+          <t>Avrupa'nın gaz ve su dağıtım ağlarına odaklanan tek ikiyıllık fuarıdır. Boru hattı tasarımı, inşaatı ve bakımı; ekipman, makine ve yazılım tedarikçileri bir arada. 7.000 m² kapalı alanda 7 teknik konferans ve 50 konuşmacı.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>info@pipelineandgasexpo.com</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>108+ Katılımcı, 2.500+ Ziyaretçi</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://www.pipelineandgasexpo.com</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gastech 2026</t>
+          <t>LNGCON 2026 – Int'l LNG Congress</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14–17 Eylül</t>
+          <t>LNGCON Barselona</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tayland</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>asia</t>
+          <t>Barselona</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>İspanya</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>lng</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>dmg events</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>BITEC</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.gastechevent.com</t>
+          <t>Barcelona (Enagás Sponsorluğu)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Check official site</t>
+          <t>BGS Group</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.98</v>
+          <t>https://lngcongress.com</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Davetiye / Kayıt tabanlı (fiyat talep üzerine)</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.gastechevent.com/visit/visitor-registration/</t>
-        </is>
-      </c>
+          <t>12. edisyonunda 390'dan fazla LNG sektörü liderini bir araya getiren kapalı kapı kongresidir. Üretim, taşımacılık, ticaret ve yeniden gazlaştırma alanlarında B2B görüşmeleri. 11 Mart'ta Barcelona LNG Terminaline teknik ziyaret.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>info@bgs.group</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>390+ LNG Lideri, Kapalı Kongre</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>https://lngcongress.com</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADIPEC 2026</t>
+          <t>MEOS 2026 – Middle East Oil, Gas &amp; Geosciences Show</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2–5 Kasım</t>
+          <t>MEOS Manama</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bahreyn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>gcc</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>gcc</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Bahrain International Exhibition &amp; Convention Centre</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SPE / dmg events</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://www.meos-bahrain.com</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Ziyaretçi kaydı ücretsiz; Konferans delege: web sitesinde</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>İkiyılda bir Bahreyn'de düzenlenen Orta Doğu'nun en köklü petrol, gaz ve jeobilim fuarıdır. Arama ve üretim teknolojileri, gaz işleme, boru hattı sistemleri ve endüstriyel ekipmanlar sergilenmektedir. GCC gaz sektörünün temel buluşma noktalarından biridir.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>meos@dmgevents.com</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5.000+ Ziyaretçi, 180+ Katılımcı</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://www.meos-bahrain.com</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ABW Sofia 2026 – Architectural Building Week</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ABW Sofia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sofya</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bulgaristan</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>boiler</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Inter Expo Center, 147 Tsarigradsko Shose</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>IEC Inter Expo Center</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://iec.bg</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Ziyaretçi girişi ücretsiz</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>26. edisyonunda Bulgaristan'ın önde gelen yapı ve enerji fuarıdır. Isıtma sistemleri, brülörler, kazan teknolojileri ve gaz tesisatı ağırlıklı. GREEN ENERGY fuarıyla eş zamanlı düzenlenmektedir.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>office@iec.bg</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>200+ Katılımcı, 5.000+ Ziyaretçi</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>https://iec.bg</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OGCE 2026 – Oil &amp; Gas Connect Expo India</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OGCE Delhi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Greater Noida / Delhi NCR</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hindistan</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>India Expo Mart, Knowledge Park II</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>India Expo Mart &amp; Centre</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://gasconnectexpo.com</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Ziyaretçi ücretsiz; delege kaydı web sitesinde</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Hindistan'ın genişleyen doğal gaz altyapısına yönelik uluslararası fuar platformudur. LNG, CNG, boru hattı teknolojileri, gaz dağıtım sistemleri, endüstriyel brülörler ve kazan sistemleri sergilenmektedir. City Gas Distribution (CGD) ağının hızla büyümesiyle kritik pazar erişim noktasıdır.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>info@gasconnectexpo.com</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Hindistan Gaz Sektörünün Büyüyen Platformu</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://gasconnectexpo.com</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ROMTHERM 2026 – Isıtma, Soğutma &amp; Gaz Tesisatı</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ROMTHERM Bükreş</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bükreş</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Romanya</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>boiler</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Romexpo B2 Pavilyonu, Bd. Marasti 65-67</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Romexpo S.A.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://romtherm.ro/en</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Ziyaretçi girişi ücretsiz (ön kayıt önerilir)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Romanya'nın en köklü ısıtma ve tesisat fuarıdır (29. edisyon). Viessmann, Buderus, Ferroli, Ariston gibi önde gelen kazan ve brülör üreticileri her yıl katılmaktadır. CONSTRUCT–AMBIENT EXPO ile eş zamanlı.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>info@romexpo.ro</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>200+ Katılımcı</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://romtherm.ro/en</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lisbon Energy Summit 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lisbon Energy</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Lizbon</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Portekiz</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ng</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FIL – Feira Internacional de Lisboa</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dmg events</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://www.lisbonenergyweek.com</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Delege kaydı: €500–€1.200</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>İberya yarımadası ve Portekiz Enerji Bakanlığı destekli etkinliktir. Gaz altyapısı, LNG terminalleri ve enerji verimliliği konularında oturumlar düzenlenmektedir.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>events@dmgevents.com</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2.000+ Ziyaretçi</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://www.lisbonenergyweek.com</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CONSTRUMA &amp; HUNGAROTHERM 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Construma Budapeşte</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Budapeşte</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Macaristan</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>boiler</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>HUNGEXPO Budapest Congress &amp; Exhibition Center</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Hungexpo Zrt.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://construma.hu</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Ön kayıt ile ücretsiz</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Orta-Doğu Avrupa'nın en büyük yapı ve bina mühendisliği fuarıdır. HUNGAROTHERM bölümü; kazan teknolojileri, brülörler, doğal gaz tesisatı ve HVAC çözümlerini kapsar.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>construma@hungexpo.hu</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>500+ Katılımcı, 40.000+ Ziyaretçi</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://construma.hu</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pumps &amp; Valves Antwerp 2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pumps &amp; Valves</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Antwerp</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Belçika</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>equip</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Antwerp Expo, Jan Van Rijswijcklaan 191</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Easyfairs</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://www.pumps-valves-expo.be/en</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Ziyaretçi girişi ücretsiz (ön kayıt önerilir)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Endüstriyel sıvı ve gaz teknolojilerine yönelik Avrupa'nın önde gelen ikiyıllık fuarıdır. 20 teknik masterclass, İnovasyon Galerisi ve Maintenance fuarıyla eş zamanlı.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>www.pumps-valves-expo.be</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>300+ Katılımcı, 5.000+ Ziyaretçi</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://www.pumps-valves-expo.be/en</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RET Thessaloniki 2026 – Renewable EnergyTech Expo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RET Selanik</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Selanik</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Yunanistan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ng</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Thessaloniki International Exhibition &amp; Congress Center</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TIF-HELEXPO</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://www.renewable-energytech-expo.gr/en</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>İlgili profesyonellere ücretsiz giriş</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Güneydoğu Avrupa'nın döngüsel ekonomi ve enerji geçişi alanındaki lider etkinliğidir. Gaz-hibrit sistemler, biyogaz ve akıllı enerji çözümleri sergilenmektedir.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>hello@helexpo.gr</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3.500+ Katılımcı</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://www.renewable-energytech-expo.gr/en</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tektónica Lisbon 2026 – Yapı &amp; Gaz Ekipmanları</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tektónica Lizbon</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Lizbon</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Portekiz</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>boiler</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FIL, Parque das Nações</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FIL – Feira Internacional de Lisboa</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://www.tektonica.fil.pt</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Ziyaretçi girişi ücretsiz</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Portekiz'in lider yapı ve inşaat fuarıdır. Kazan, brülör ve gaz skid tedarikçileri ile sanayi ekipman distribütörleri katılmaktadır.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>tektonica@fil.pt</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>300+ Katılımcı</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://www.tektonica.fil.pt</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8th Global LNG Forum 2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Global LNG Forum</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Barselona</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>İspanya</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>lng</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Barselona (mekan TBC)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ALJ Group</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://lng-global.com</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Delege: €1.500–€2.500 (taleple)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Küresel LNG pazarındaki gelişmelere odaklanan Avrupa merkezli LNG etkinliğidir. Jeopolitik riskler, enerji güvenliği ve altyapı yatırımları masaya yatırılmaktadır.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>info@lng-global.com</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Seçkin katılımcılar, sınırlı kontenjan</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://lng-global.com</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gas Professionals Meeting Opatija 2026 (41st)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gas Meeting Opatija</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Opatija</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Hırvatistan</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>dist</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Opatija Kongre Merkezi</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>HSUP – Croatian Gas Association</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://susret.hsup.hr/en</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Delege kaydı: Fiyat web sitesinde</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Güneydoğu Avrupa'nın en büyük uluslararası gaz konferansı ve fuarıdır (41. edisyon). Gas skid, brülör, boru hattı ve gaz ölçüm ekipmanı üreticileri sergilenmektedir.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>susret@hsup.hr</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>300+ Gaz Profesyoneli</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://susret.hsup.hr/en</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MPGC 2026 – 33rd Middle East Petroleum &amp; Gas Conference</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MPGC Dubai</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>BAE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>gcc</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>gcc</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Jumeirah Emirates Towers, Dubai</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>S&amp;P Global / ENOC</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://www.spglobal.com/energy/en/events/conferences/mpgc</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD tabanlı; S&amp;P Global web sitesinde</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Orta Doğu'nun en uzun soluklu yıllık petrol ve gaz konferansıdır (33. edisyon). HH Şeyh Ahmed bin Saeed Al Maktoum himayesinde gerçekleşir. LNG &amp; gaz dengesi, enerji güvenliği konularında bakanlık ve CEO seviyesinde paneller.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>spglobal.com/energy/events/mpgc</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NOC, IOC, Trader, Refiner Katılımı</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://www.spglobal.com/energy/en/events/conferences/mpgc</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OPES 2026 – Oman Petroleum &amp; Energy Show</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OPES Muskat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Muskat</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Umman</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>gcc</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>gcc</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>OCEC – Oman Convention &amp; Exhibition Centre</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>CONNECT – Oman Exhibitions LLC</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://omanpetroleumandenergyshow.com</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Ziyaretçi girişi ücretsiz; SPE delege web sitesinde</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Umman'ın tek entegre petrol, gaz ve enerji fuarıdır. SPE Konferansı eş zamanlı düzenlenmektedir. Gaz işleme sistemleri, pompa &amp; kompresörler, endüstriyel brülörler ve gaz skid ekipmanları sergilenmektedir.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>info@connectthroughus.com</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>180+ Katılımcı, 6.000+ Ziyaretçi</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://omanpetroleumandenergyshow.com</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gas, LNG &amp; The Future of Energy 2026 (Wood Mackenzie)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WoodMac Gas &amp; LNG</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>İngiltere</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>lng</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Wood Mackenzie</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://www.woodmac.com/events/gas-lng-future-energy</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Fiyat kayıt sayfasında</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Wood Mackenzie'nin yıllık Gaz &amp; LNG konferansı. Avrupa gaz toplayıcıları, Asya LNG alıcıları ve yatırım bankaları bir araya gelir. Jeopolitik riskler ve fiyat oynaklığı gündemdedir.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>events@woodmac.com</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>300+ Katılımcı, 142+ Konuşmacı</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://www.woodmac.com/events/gas-lng-future-energy</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Baku Energy Week 2026 – Caspian Oil &amp; Gas + Caspian Power</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Baku Energy Week</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bakü</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Azerbaycan</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>turkic</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>gcc</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Baku Expo Center, 515 H. Aliyev Ave.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Iteca Caspian LLC / SOCAR</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://caspianoilgas.az/en</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Ziyaretçi kaydı ücretsiz; Forum: fiyat taleple</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Hazar bölgesinin en prestijli enerji etkinliğidir. Azerbaycan Cumhurbaşkanı açılışa katılmaktadır. SOCAR, bp, TotalEnergies ve Equinor katılır. Gaz sahası geliştirme, boru hattı güvenliği ve gaz işleme ana gündem başlıklarıdır.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>info@iteca.az</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>300+ Katılımcı, 37 Ülke</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://caspianoilgas.az/en</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GTC 2026 – Gas Technology Conference (WLGA)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GTC WLGA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Avrupa</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Avrupa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>lpg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>WLGA</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://www.worldliquidgas.org</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Kayıt fiyatları açıklanacak</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>LPG ve yenilenebilir DME endüstrisinde teknoloji ve inovasyona odaklanan tek küresel konferanstır. Global İnovasyon Ödülü yarışması da düzenlenmektedir.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>wlga@worldliquidgas.org</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Global LPG endüstrisi liderleri</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://www.worldliquidgas.org</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FOREN 2026 – WEC Central &amp; Eastern Europe Energy Forum</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FOREN Neptun</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Neptun</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Romanya</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ng</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Neptun Uluslararası Kongre Merkezi, Karadeniz Kıyısı</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>WEC Romanian National Committee</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://www.foren.ro</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Delege kaydı: Fiyat taleple</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Romanya Hükümeti himayesinde WEC koordinasyonuyla ikiyılda bir düzenlenen bölgenin en prestijli enerji forumudur. Kazanlar, borular, valfler ve gaz ekipmanları sergi kategorilerindedir.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>secretariat@wec-romania.ro</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>400+ Enerji Uzmanı</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://www.foren.ro</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gas India Expo 2026 – GIE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gas India Expo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Greater Noida / Delhi NCR</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Hindistan</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>India Expo Centre and Mart, Greater Noida</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Indian Exhibition Services</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://www.gasindiaexpo.com</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Stand ve ziyaretçi kaydı web sitesinde</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Doğal gaz, LNG, hidrojen ve endüstriyel gaz üretimine yönelik uluslararası fuar platformudur. CNG/LNG dolum ekipmanları, boru hatları ve gaz ölçüm cihazları ile endüstriyel brülörler ana sergi kategorileridir.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>info@gasindiaexpo.com</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Uluslararası Katılım</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://www.gasindiaexpo.com</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Gastech Exhibition &amp; Conference 2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Gastech Bangkok</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tayland</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BITEC – Bangkok International Trade &amp; Exhibition Centre</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>dmg events</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>ADNEC Centre Abu Dhabi</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://www.gastechevent.com</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Sergi ücretsiz (kayıt gerekli); Konferans: web sitesinde</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>54. yılında dünyanın en büyük doğal gaz, LNG ve hidrojen konferans &amp; fuarıdır. 20 ülke pavilyonu, 4 özel sergi bölümü ve 1.000+ konuşmacı. Avrupa'lı gaz skid ve brülör üreticileri için Asya pazarına açılımın en etkili platformudur.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>gastech@dmgevents.com</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1.000+ Katılımcı, 50.000+ Ziyaretçi, 150+ Ülke</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://www.gastechevent.com</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KIOGE 2026 – 30th Kazakhstan Int'l Oil &amp; Gas Exhibition</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>KIOGE Almatı</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Almatı</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kazakistan</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>turkic</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>gcc</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Atakent International Exhibition Centre, 42 Timiryazev Str.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Iteca Kazakhstan / KAZENERGY</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://kioge.kz/en</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ziyaretçi kaydı ücretsiz; konferans web sitesinde</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>30. yılında Orta Asya'nın en büyük petrol &amp; gaz fuarıdır. KazMunayGas, Tengizchevroil ve NCOC destekli. Kazan &amp; ısıtma teknolojileri, gaz ölçüm &amp; arıtma ekipmanları sergilenmektedir.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>contact@iteca.kz</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>350+ Katılımcı, 5.000+ Ziyaretçi</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://kioge.kz/en</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Liquid Gas Week 2026 – Istanbul</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Liquid Gas Week İstanbul</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>lpg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Istanbul Congress Center (ICC)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>WLGA (World Liquid Gas Association)</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://www.liquidgasweek.com/istanbul-2026</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>WLGA üyelerine %20 indirim; Delege ~€1.500–€3.000</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>LPG sektörünün en büyük yıllık buluşmasıdır. IEA Başkanı Dr. Fatih Birol açılış konuşmacısıdır. Sergi alanının %90'ı dolu.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>events@worldliquidgas.org</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2.000+ Profesyonel, Küresel Sergi</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://www.liquidgasweek.com/istanbul-2026</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Energetika 2026 – International Energy Fair Belgrade</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Energetika Belgrad</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Belgrad</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sırbistan</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ng</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Belgrade Fair Grounds, Bulevar vojvode Mišića 14</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Beogradski sajam (Belgrade Fair)</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://www.sajamenergetike.rs</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ziyaretçi girişi ücretsiz</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>21. edisyonunda UFI lisanslı Sırbistan'ın en büyük enerji fuarıdır. Gaz türbinleri, buhar kazanları ve endüstriyel gaz ekipmanı üreticileri katılmaktadır.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>energetika@sajam.rs</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>80+ Katılımcı</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://www.sajamenergetike.rs</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ADIPEC 2026 – Abu Dhabi Int'l Petroleum Exhibition &amp; Conference</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ADIPEC Abu Dabi</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Abu Dabi</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>BAE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>gcc</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>gcc</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ADNEC – Abu Dhabi National Exhibition Centre</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dmg events / ADNOC</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>https://www.adipec.com</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Check official site</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ziyaretçi kaydı ücretsiz; Konferans: web sitesinde</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Dünyanın en büyük enerji etkinliklerinden biridir. 54 enerji şirketi, 30 ülke pavilyonu ve 12 konferans programı. Endüstriyel kazan &amp; brülör sistemleri, gaz ölçüm &amp; skid ekipmanları ile küresel devler aynı çatıda.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>adipec@dmgevents.com</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2.250+ Katılımcı, 239.000+ Ziyaretçi</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>https://www.adipec.com</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OSEA 2026 – Offshore South East Asia</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OSEA Singapur</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Singapur</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Singapur</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Marina Bay Sands Expo &amp; Convention Centre</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Singapore Exhibition Services Pte Ltd</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://www.osea-offshore.com</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ziyaretçi kaydı ücretsiz; Konferans: web sitesinde</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>49 yıllık geçmişiyle Asya-Pasifik'in köklü petrol &amp; gaz fuarıdır. LNG işleme, taşıma terminalleri, boru hattı ekipmanları ve endüstriyel gaz sistemleri sergilenmektedir.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>osea@sesallworld.com</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>500+ Katılımcı, 70+ Ülke, 18.000+ Uzman</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://www.osea-offshore.com</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>26th World LNG Summit &amp; Awards 2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>World LNG Summit</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>lng</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>İstanbul (mekan TBC)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Energy Council</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://www.worldlngsummit.com</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Delege kaydı: Fiyat taleple</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Küresel LNG endüstrisinin yıllık buluşma noktasıdır. Enerji güvenliği ve karbonsuzlaşma dengesini ele almaktadır. Global LNG Ödülleri de bu etkinlikte verilmektedir.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>info@worldlngsummit.com</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1.000+ LNG Profesyoneli</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://www.worldlngsummit.com</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>seed_html</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>seeded</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -634,7 +634,11 @@
       <c r="S2" t="n">
         <v>0.8</v>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -730,7 +734,11 @@
       <c r="S3" t="n">
         <v>0.8</v>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -826,7 +834,11 @@
       <c r="S4" t="n">
         <v>0.8</v>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -922,7 +934,11 @@
       <c r="S5" t="n">
         <v>0.8</v>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1018,7 +1034,11 @@
       <c r="S6" t="n">
         <v>0.8</v>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1114,7 +1134,11 @@
       <c r="S7" t="n">
         <v>0.8</v>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1210,7 +1234,11 @@
       <c r="S8" t="n">
         <v>0.8</v>
       </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1306,7 +1334,11 @@
       <c r="S9" t="n">
         <v>0.8</v>
       </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1402,7 +1434,11 @@
       <c r="S10" t="n">
         <v>0.8</v>
       </c>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1498,7 +1534,11 @@
       <c r="S11" t="n">
         <v>0.8</v>
       </c>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1594,7 +1634,11 @@
       <c r="S12" t="n">
         <v>0.8</v>
       </c>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1690,7 +1734,11 @@
       <c r="S13" t="n">
         <v>0.8</v>
       </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1786,7 +1834,11 @@
       <c r="S14" t="n">
         <v>0.8</v>
       </c>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1882,7 +1934,11 @@
       <c r="S15" t="n">
         <v>0.8</v>
       </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1978,7 +2034,11 @@
       <c r="S16" t="n">
         <v>0.8</v>
       </c>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2074,7 +2134,11 @@
       <c r="S17" t="n">
         <v>0.8</v>
       </c>
-      <c r="T17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2170,7 +2234,11 @@
       <c r="S18" t="n">
         <v>0.8</v>
       </c>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2266,7 +2334,11 @@
       <c r="S19" t="n">
         <v>0.8</v>
       </c>
-      <c r="T19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2362,7 +2434,11 @@
       <c r="S20" t="n">
         <v>0.8</v>
       </c>
-      <c r="T20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2458,7 +2534,11 @@
       <c r="S21" t="n">
         <v>0.8</v>
       </c>
-      <c r="T21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2554,7 +2634,11 @@
       <c r="S22" t="n">
         <v>0.8</v>
       </c>
-      <c r="T22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2650,7 +2734,11 @@
       <c r="S23" t="n">
         <v>0.8</v>
       </c>
-      <c r="T23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2746,7 +2834,11 @@
       <c r="S24" t="n">
         <v>0.8</v>
       </c>
-      <c r="T24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2842,7 +2934,11 @@
       <c r="S25" t="n">
         <v>0.8</v>
       </c>
-      <c r="T25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2938,7 +3034,11 @@
       <c r="S26" t="n">
         <v>0.8</v>
       </c>
-      <c r="T26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3034,7 +3134,11 @@
       <c r="S27" t="n">
         <v>0.8</v>
       </c>
-      <c r="T27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3130,7 +3234,11 @@
       <c r="S28" t="n">
         <v>0.8</v>
       </c>
-      <c r="T28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:57:30+00:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-03T08:57:30+00:00</t>
+          <t>2026-06-04T08:22:45+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-04T08:22:45+00:00</t>
+          <t>2026-06-05T08:10:21+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-05T08:10:21+00:00</t>
+          <t>2026-06-06T06:55:51+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-06T06:55:51+00:00</t>
+          <t>2026-06-07T07:56:54+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-07T07:56:54+00:00</t>
+          <t>2026-06-08T08:57:34+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-08T08:57:34+00:00</t>
+          <t>2026-06-09T07:54:27+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-09T07:54:27+00:00</t>
+          <t>2026-06-10T08:11:03+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-10T08:11:03+00:00</t>
+          <t>2026-06-11T08:48:34+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-11T08:48:34+00:00</t>
+          <t>2026-06-12T08:27:21+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-12T08:27:21+00:00</t>
+          <t>2026-06-13T07:51:13+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-13T07:51:13+00:00</t>
+          <t>2026-06-14T08:17:41+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-14T08:17:41+00:00</t>
+          <t>2026-06-15T10:26:06+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-15T10:26:06+00:00</t>
+          <t>2026-06-16T09:29:11+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-16T09:29:11+00:00</t>
+          <t>2026-06-17T09:04:27+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-17T09:04:27+00:00</t>
+          <t>2026-06-18T08:49:29+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-18T08:49:29+00:00</t>
+          <t>2026-06-19T09:07:28+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-19T09:07:28+00:00</t>
+          <t>2026-06-20T07:53:08+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-20T07:53:08+00:00</t>
+          <t>2026-06-21T08:36:32+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-21T08:36:32+00:00</t>
+          <t>2026-06-22T09:50:00+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-22T09:50:00+00:00</t>
+          <t>2026-06-23T07:52:42+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-23T07:52:42+00:00</t>
+          <t>2026-06-24T07:44:34+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-24T07:44:34+00:00</t>
+          <t>2026-06-25T07:49:38+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-25T07:49:38+00:00</t>
+          <t>2026-06-26T07:56:59+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-26T07:56:59+00:00</t>
+          <t>2026-06-27T06:55:38+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-27T06:55:38+00:00</t>
+          <t>2026-06-28T07:53:01+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-28T07:53:01+00:00</t>
+          <t>2026-06-29T09:01:09+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-29T09:01:09+00:00</t>
+          <t>2026-06-30T07:56:36+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-30T07:56:36+00:00</t>
+          <t>2026-07-01T08:16:23+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-01T08:16:23+00:00</t>
+          <t>2026-07-02T07:35:29+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-02T07:35:29+00:00</t>
+          <t>2026-07-03T07:24:29+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-03T07:24:29+00:00</t>
+          <t>2026-07-04T06:49:26+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-04T06:49:26+00:00</t>
+          <t>2026-07-05T07:30:10+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-05T07:30:10+00:00</t>
+          <t>2026-07-06T08:25:01+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-06T08:25:01+00:00</t>
+          <t>2026-07-07T07:42:26+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-07T07:42:26+00:00</t>
+          <t>2026-07-08T06:31:01+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-08T06:31:01+00:00</t>
+          <t>2026-07-09T07:39:21+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-09T07:39:21+00:00</t>
+          <t>2026-07-10T07:38:47+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-10T07:38:47+00:00</t>
+          <t>2026-07-11T06:17:09+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-11T06:17:09+00:00</t>
+          <t>2026-07-12T06:36:51+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-12T06:36:51+00:00</t>
+          <t>2026-07-13T06:57:48+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-13T06:57:48+00:00</t>
+          <t>2026-07-14T06:13:31+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-14T06:13:31+00:00</t>
+          <t>2026-07-15T06:17:59+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-15T06:17:59+00:00</t>
+          <t>2026-07-16T06:21:47+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-16T06:21:47+00:00</t>
+          <t>2026-07-17T06:19:47+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-17T06:19:47+00:00</t>
+          <t>2026-07-18T06:07:41+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-18T06:07:41+00:00</t>
+          <t>2026-07-19T06:32:54+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-19T06:32:54+00:00</t>
+          <t>2026-07-20T06:50:36+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-20T06:50:36+00:00</t>
+          <t>2026-07-21T06:32:00+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-21T06:32:00+00:00</t>
+          <t>2026-07-22T06:31:41+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-22T06:31:41+00:00</t>
+          <t>2026-07-23T06:33:02+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-23T06:33:02+00:00</t>
+          <t>2026-07-24T06:28:47+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-24T06:28:47+00:00</t>
+          <t>2026-07-25T06:20:30+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-25T06:20:30+00:00</t>
+          <t>2026-07-26T06:40:01+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-26T06:40:01+00:00</t>
+          <t>2026-07-27T07:36:16+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-27T07:36:16+00:00</t>
+          <t>2026-07-28T06:29:36+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-28T06:29:36+00:00</t>
+          <t>2026-07-29T06:34:24+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-29T06:34:24+00:00</t>
+          <t>2026-07-30T06:31:00+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-30T06:31:00+00:00</t>
+          <t>2026-07-31T06:47:36+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-31T06:47:36+00:00</t>
+          <t>2026-08-01T06:32:14+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-01T06:32:14+00:00</t>
+          <t>2026-08-02T06:36:04+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-02T06:36:04+00:00</t>
+          <t>2026-08-03T07:31:26+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-03T07:31:26+00:00</t>
+          <t>2026-08-04T06:30:05+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-04T06:30:05+00:00</t>
+          <t>2026-08-05T06:31:12+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-05T06:31:12+00:00</t>
+          <t>2026-08-06T06:34:29+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-06T06:34:29+00:00</t>
+          <t>2026-08-07T05:42:32+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-07T05:42:32+00:00</t>
+          <t>2026-08-08T05:00:07+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:07+00:00</t>
+          <t>2026-08-09T05:08:57+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-09T05:08:57+00:00</t>
+          <t>2026-08-10T05:36:03+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-10T05:36:03+00:00</t>
+          <t>2026-08-11T05:12:57+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-11T05:12:57+00:00</t>
+          <t>2026-08-12T05:39:26+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-12T05:39:26+00:00</t>
+          <t>2026-08-13T05:42:02+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-13T05:42:02+00:00</t>
+          <t>2026-08-14T05:39:45+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-14T05:39:45+00:00</t>
+          <t>2026-08-15T04:34:24+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-15T04:34:24+00:00</t>
+          <t>2026-08-16T04:38:51+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-16T04:38:51+00:00</t>
+          <t>2026-08-17T04:45:38+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-17T04:45:38+00:00</t>
+          <t>2026-08-18T04:38:08+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-18T04:38:08+00:00</t>
+          <t>2026-08-19T04:40:04+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-19T04:40:04+00:00</t>
+          <t>2026-08-20T04:39:48+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-20T04:39:48+00:00</t>
+          <t>2026-08-21T04:41:34+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-21T04:41:34+00:00</t>
+          <t>2026-08-22T04:35:56+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-22T04:35:56+00:00</t>
+          <t>2026-08-23T04:40:07+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-23T04:40:07+00:00</t>
+          <t>2026-08-24T04:49:11+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-24T04:49:11+00:00</t>
+          <t>2026-08-25T04:41:30+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-25T04:41:30+00:00</t>
+          <t>2026-08-26T04:42:27+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-26T04:42:27+00:00</t>
+          <t>2026-08-27T15:03:24+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-27T15:03:24+00:00</t>
+          <t>2026-08-28T16:26:24+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-28T16:26:24+00:00</t>
+          <t>2026-08-29T10:55:21+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-29T10:55:21+00:00</t>
+          <t>2026-08-30T09:49:43+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-30T09:49:43+00:00</t>
+          <t>2026-08-31T10:40:44+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:44+00:00</t>
+          <t>2026-09-01T09:16:34+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-01T09:16:34+00:00</t>
+          <t>2026-09-02T08:35:19+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-02T08:35:19+00:00</t>
+          <t>2026-09-03T08:43:52+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-03T08:43:52+00:00</t>
+          <t>2026-09-04T08:39:14+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-04T08:39:14+00:00</t>
+          <t>2026-09-05T08:11:49+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-05T08:11:49+00:00</t>
+          <t>2026-09-06T08:28:50+00:00</t>
         </is>
       </c>
     </row>
